--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6796-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6796-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3790772-D86F-4C82-A4EA-011BAFEABEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1A49DFA-3504-4738-B535-AF57E9BA30BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{37106CAF-B906-48FA-95A6-789FAC4985F8}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C1ED9316-E296-4BDB-8138-220173C729EA}"/>
   </bookViews>
   <sheets>
     <sheet name="6796-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1421,25 +1421,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D07E40C9-1374-495B-A7A2-AAA35134626B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB873E3-B860-41E0-B21B-1FC996813065}">
   <dimension ref="A1:X10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="4" width="6.625" customWidth="1"/>
-    <col min="5" max="5" width="6.25" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
-    <col min="7" max="9" width="6.25" customWidth="1"/>
-    <col min="10" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1473,7 +1472,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1509,7 +1508,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1561,7 +1560,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1629,7 +1628,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1701,7 +1700,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1773,7 +1772,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1845,7 +1844,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1917,7 +1916,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -1989,7 +1988,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35" t="s">
         <v>33</v>
       </c>
